--- a/mock/raw/IPQC01.xlsx
+++ b/mock/raw/IPQC01.xlsx
@@ -2133,7 +2133,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>실링</t>
+          <t>사이드 실링</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2197,7 +2197,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="6" t="n"/>
       <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
+      <c r="C28" s="7" t="n"/>
       <c r="D28" s="4" t="inlineStr">
         <is>
           <t>both</t>
@@ -2259,7 +2259,11 @@
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="6" t="n"/>
       <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>프리 실링</t>
+        </is>
+      </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
           <t>both</t>
@@ -2321,7 +2325,11 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="6" t="n"/>
       <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>사이드 실링</t>
+        </is>
+      </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
           <t>both</t>
@@ -2379,7 +2387,6 @@
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="6" t="n"/>
       <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
       <c r="D31" s="4" t="inlineStr">
         <is>
           <t>both</t>
@@ -2653,7 +2660,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>실링</t>
+          <t>사이드 실링</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2715,9 +2722,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
+    <mergeCell ref="C30:C31"/>
     <mergeCell ref="A4:A35"/>
-    <mergeCell ref="C27:C31"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="B23:B26"/>
     <mergeCell ref="C9:C12"/>
@@ -2726,6 +2733,7 @@
     <mergeCell ref="B19:B22"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="A1:P1"/>
+    <mergeCell ref="C27:C28"/>
     <mergeCell ref="C4:C8"/>
     <mergeCell ref="C32:C33"/>
     <mergeCell ref="C23:C26"/>
